--- a/MT4_UM1.xlsx
+++ b/MT4_UM1.xlsx
@@ -8,12 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yiming.chong\Documents\GitHub\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD046CA-5C24-42B2-8BD4-2402021B65CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF593C9-32AD-45F4-851F-76DE48932C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Forex1" sheetId="1" r:id="rId1"/>
+    <sheet name="Forex2" sheetId="3" r:id="rId2"/>
+    <sheet name="Gold1" sheetId="5" r:id="rId3"/>
+    <sheet name="Oil1" sheetId="9" r:id="rId4"/>
+    <sheet name="Indices1" sheetId="10" r:id="rId5"/>
+    <sheet name="Indices2" sheetId="11" r:id="rId6"/>
+    <sheet name="Indices3" sheetId="12" r:id="rId7"/>
+    <sheet name="Indices4" sheetId="13" r:id="rId8"/>
+    <sheet name="Indices5" sheetId="14" r:id="rId9"/>
+    <sheet name="Indices6" sheetId="15" r:id="rId10"/>
+    <sheet name="Indices7" sheetId="16" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="52">
   <si>
     <t>CompanyName</t>
   </si>
@@ -65,31 +75,133 @@
     <t>ProfileName</t>
   </si>
   <si>
-    <t>vantage</t>
-  </si>
-  <si>
-    <t>08a6e9c0-a0d5-42f6-942e-94b42e0e616d</t>
-  </si>
-  <si>
     <t>ServerName</t>
   </si>
   <si>
-    <t>Staging</t>
-  </si>
-  <si>
-    <t>MT5</t>
-  </si>
-  <si>
-    <t>bc3c7a34-e2d0-482a-bb15-74b961535ff5</t>
-  </si>
-  <si>
-    <t>Admin Vantage</t>
-  </si>
-  <si>
-    <t>testing</t>
-  </si>
-  <si>
-    <t>paul.shih@unicornfintech.com</t>
+    <t>ToDay</t>
+  </si>
+  <si>
+    <t>FromHour</t>
+  </si>
+  <si>
+    <t>ToHour</t>
+  </si>
+  <si>
+    <t>FromMinute</t>
+  </si>
+  <si>
+    <t>ToMinute</t>
+  </si>
+  <si>
+    <t>Tiers</t>
+  </si>
+  <si>
+    <t>T1=0:200;</t>
+  </si>
+  <si>
+    <t>SessionTitle</t>
+  </si>
+  <si>
+    <t>TiersDisplay</t>
+  </si>
+  <si>
+    <t>0➜∞[200];</t>
+  </si>
+  <si>
+    <t>FromDay</t>
+  </si>
+  <si>
+    <t>T1=0:0.5;</t>
+  </si>
+  <si>
+    <t>0➜∞[0.5];</t>
+  </si>
+  <si>
+    <t>alphatick</t>
+  </si>
+  <si>
+    <t>fa26617c-1f9e-44ef-9ec9-ae2384091371</t>
+  </si>
+  <si>
+    <t>Live</t>
+  </si>
+  <si>
+    <t>MT4</t>
+  </si>
+  <si>
+    <t>2ba7d46d-4bcc-4410-9229-378bd10e70c1</t>
+  </si>
+  <si>
+    <t>MT4 Support</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Forex - Fri 23:00-24:00, Mon 00:00-00:30</t>
+  </si>
+  <si>
+    <t>mt4@ultimamarkets.com</t>
+  </si>
+  <si>
+    <t>UM1 - General - Forex</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Forex (AUDCNH) - Fri 23:00-24:00, Mon 03:00-03:30</t>
+  </si>
+  <si>
+    <t>UM1 - General - AUDCNH</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Gold - Fri 23:00-24:00, Mon 01:00-01:30</t>
+  </si>
+  <si>
+    <t>UM1 - General - Gold</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Oil - Fri 23:00-24:00, Mon 01:00-01:30</t>
+  </si>
+  <si>
+    <t>UM1 - General - Oil</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Indices - Fri 23:00-24:00, Mon 01:00-01:30</t>
+  </si>
+  <si>
+    <t>UM1 - General - Indices</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Indices (HK50 / HK50ft) - Fri 20:00-21:00, Mon 03:15-03:45</t>
+  </si>
+  <si>
+    <t>UM1 - General - Indices (HK50 / HK50ft)</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Indices (UK100 / UK100ft) - Fri 22:00-23:00, Mon 01:05-01:35</t>
+  </si>
+  <si>
+    <t>UM1 - General - Indices (UK100 / UK100ft)</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Indices (GER40 / GER40ft) - Fri 22:00-23:00, Mon 02:15-02:45</t>
+  </si>
+  <si>
+    <t>UM1 - General - Indices (GER40 / GER40ft)</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Indices (FRA40ft) - Fri 22:00-23:00, Mon 09:00-09:30</t>
+  </si>
+  <si>
+    <t>UM1 - General - Indices (FRA40ft)</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Indices (VIX) - Fri 22:15-23:15, Mon 01:00-01:30</t>
+  </si>
+  <si>
+    <t>UM1 - General - Indices (VIX)</t>
+  </si>
+  <si>
+    <t>[News + General] - UM1 - Indices (CHINA50 / CHINA50ft) - Fri 21:45-22:45, Mon 03:00-03:30</t>
+  </si>
+  <si>
+    <t>UM1 - General - Indices (CHINA50 / CHINA50ft)</t>
   </si>
 </sst>
 </file>
@@ -407,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -422,7 +534,7 @@
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,7 +545,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -453,37 +565,1501 @@
       <c r="J1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>23</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A97939-2805-41FD-B680-B53CD297F10A}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>9</v>
       </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>22</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>15</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50532A11-BB1D-4F26-BBEE-FF3CAFF17BE2}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
         <v>10</v>
       </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
       <c r="C2">
-        <v>1326</v>
+        <v>1051</v>
       </c>
       <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>18</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>21</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <v>45</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBFB7EA-40D2-4AEF-AE16-9C6A9ACF0727}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
         <v>12</v>
       </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
       <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>23</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86B2852-C16D-4326-8626-1C545ED09338}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
         <v>13</v>
       </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
       <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>23</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ABB095-35F2-4820-BA7D-AACDF5AC29ED}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
         <v>14</v>
       </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
       <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>11</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>23</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A64BA9-AE49-4601-BDB8-368EE6FA41C6}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
       <c r="H2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>12</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>23</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644856BC-020F-4C9A-8C44-C2C911A21A97}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>45</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F213CA8B-C6C2-4E7B-A814-8A18CEB0E85C}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>22</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A58BA4B6-30AC-4566-AC69-57CCCF3E997A}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>22</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>45</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C27AB6-C119-4240-85FC-9A3D905F4959}">
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2">
-        <v>167</v>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>22</v>
+      </c>
+      <c r="N2">
+        <v>9</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/MT4_UM1.xlsx
+++ b/MT4_UM1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yiming.chong\Documents\GitHub\automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaiwei.chin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF593C9-32AD-45F4-851F-76DE48932C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528DA312-5F9E-4AF8-9100-3786FA5139C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25425" yWindow="375" windowWidth="24285" windowHeight="13905" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Forex1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="52">
   <si>
     <t>CompanyName</t>
   </si>
@@ -208,10 +208,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -519,22 +525,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -593,7 +603,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -652,7 +662,244 @@
         <v>19</v>
       </c>
     </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>8</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -660,22 +907,22 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A97939-2805-41FD-B680-B53CD297F10A}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5546875" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -734,7 +981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -790,6 +1037,242 @@
         <v>49</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>17</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>22</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>15</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>17</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>22</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>15</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>17</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>15</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>17</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>22</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>15</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -801,22 +1284,22 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50532A11-BB1D-4F26-BBEE-FF3CAFF17BE2}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="42.5546875" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +1358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -931,6 +1414,242 @@
         <v>51</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>18</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>45</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>18</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>21</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>45</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>51</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>18</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>21</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>45</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>51</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>18</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>21</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>45</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>51</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -942,22 +1661,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBFB7EA-40D2-4AEF-AE16-9C6A9ACF0727}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1016,7 +1735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1075,7 +1794,244 @@
         <v>19</v>
       </c>
     </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>9</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1083,22 +2039,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86B2852-C16D-4326-8626-1C545ED09338}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1157,7 +2114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1216,7 +2173,244 @@
         <v>19</v>
       </c>
     </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S6" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1224,22 +2418,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ABB095-35F2-4820-BA7D-AACDF5AC29ED}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +2492,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1357,7 +2551,244 @@
         <v>22</v>
       </c>
     </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1365,22 +2796,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A64BA9-AE49-4601-BDB8-368EE6FA41C6}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +2870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1495,6 +2926,242 @@
         <v>39</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1506,22 +3173,23 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644856BC-020F-4C9A-8C44-C2C911A21A97}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="72.5546875" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +3248,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1636,6 +3304,242 @@
         <v>41</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>13</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>20</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>45</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>20</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1647,22 +3551,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F213CA8B-C6C2-4E7B-A814-8A18CEB0E85C}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" customWidth="1"/>
+    <col min="8" max="8" width="74.88671875" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1721,7 +3625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1777,6 +3681,242 @@
         <v>43</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>14</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>14</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1788,22 +3928,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A58BA4B6-30AC-4566-AC69-57CCCF3E997A}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.77734375" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1862,7 +4002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1918,6 +4058,242 @@
         <v>45</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>15</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>45</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1929,22 +4305,22 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C27AB6-C119-4240-85FC-9A3D905F4959}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.88671875" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2003,7 +4379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -2059,6 +4435,242 @@
         <v>47</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>16</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>22</v>
+      </c>
+      <c r="N3">
+        <v>9</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>16</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>22</v>
+      </c>
+      <c r="N4">
+        <v>9</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1051</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>16</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>9</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1051</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>22</v>
+      </c>
+      <c r="N6">
+        <v>9</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>47</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>

--- a/MT4_UM1.xlsx
+++ b/MT4_UM1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaiwei.chin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chong\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528DA312-5F9E-4AF8-9100-3786FA5139C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6F5FCA-2EE0-47F1-A46F-8EE7FFF75E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25425" yWindow="375" windowWidth="24285" windowHeight="13905" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12800" yWindow="0" windowWidth="12800" windowHeight="16000" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Forex1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="52">
   <si>
     <t>CompanyName</t>
   </si>
@@ -525,26 +525,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="57.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -603,7 +603,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -635,13 +635,13 @@
         <v>8</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -694,13 +694,13 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -721,7 +721,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -753,13 +753,13 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -812,13 +812,13 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -871,13 +871,13 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -895,6 +895,301 @@
         <v>31</v>
       </c>
       <c r="S6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" t="s">
+        <v>31</v>
+      </c>
+      <c r="S7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>23</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>8</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>23</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>16</v>
+      </c>
+      <c r="R10" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>23</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>16</v>
+      </c>
+      <c r="R11" t="s">
+        <v>31</v>
+      </c>
+      <c r="S11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -907,22 +1202,22 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A97939-2805-41FD-B680-B53CD297F10A}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.5546875" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.54296875" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -981,7 +1276,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1013,19 +1308,19 @@
         <v>17</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>1</v>
       </c>
       <c r="O2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>30</v>
@@ -1040,7 +1335,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1072,19 +1367,19 @@
         <v>17</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
       <c r="O3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>30</v>
@@ -1099,7 +1394,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1131,19 +1426,19 @@
         <v>17</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>30</v>
@@ -1158,7 +1453,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1190,19 +1485,19 @@
         <v>17</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>1</v>
       </c>
       <c r="O5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>30</v>
@@ -1217,7 +1512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1249,19 +1544,19 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
       <c r="O6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>30</v>
@@ -1273,6 +1568,301 @@
         <v>49</v>
       </c>
       <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>17</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>22</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>15</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>49</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>17</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>22</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>15</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>49</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>17</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>22</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>15</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>49</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>17</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>22</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>15</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>49</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>17</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>22</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>15</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>49</v>
+      </c>
+      <c r="S11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1284,22 +1874,22 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50532A11-BB1D-4F26-BBEE-FF3CAFF17BE2}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="42.5546875" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="42.54296875" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1358,7 +1948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1390,19 +1980,19 @@
         <v>18</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>30</v>
@@ -1417,7 +2007,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1449,19 +2039,19 @@
         <v>18</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>30</v>
@@ -1476,7 +2066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1508,19 +2098,19 @@
         <v>18</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>30</v>
@@ -1535,7 +2125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1567,19 +2157,19 @@
         <v>18</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>30</v>
@@ -1594,7 +2184,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1626,19 +2216,19 @@
         <v>18</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>30</v>
@@ -1650,6 +2240,301 @@
         <v>51</v>
       </c>
       <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>22</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>45</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>51</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>22</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>45</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>51</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>18</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>22</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>45</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>51</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>18</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>22</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>45</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>51</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>18</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>22</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>45</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>51</v>
+      </c>
+      <c r="S11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1661,22 +2546,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBFB7EA-40D2-4AEF-AE16-9C6A9ACF0727}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1735,7 +2620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1767,13 +2652,13 @@
         <v>9</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>3</v>
@@ -1794,7 +2679,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1826,13 +2711,13 @@
         <v>9</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>3</v>
@@ -1853,7 +2738,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1885,13 +2770,13 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -1912,7 +2797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1944,13 +2829,13 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -1971,7 +2856,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -2003,13 +2888,13 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>3</v>
@@ -2027,6 +2912,301 @@
         <v>33</v>
       </c>
       <c r="S6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" t="s">
+        <v>33</v>
+      </c>
+      <c r="S7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>23</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>9</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R9" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>23</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>16</v>
+      </c>
+      <c r="R10" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>9</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>23</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>16</v>
+      </c>
+      <c r="R11" t="s">
+        <v>33</v>
+      </c>
+      <c r="S11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2039,23 +3219,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86B2852-C16D-4326-8626-1C545ED09338}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2114,7 +3294,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -2146,13 +3326,13 @@
         <v>10</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -2173,7 +3353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -2205,13 +3385,13 @@
         <v>10</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -2232,7 +3412,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2264,13 +3444,13 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -2291,7 +3471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2323,13 +3503,13 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -2350,7 +3530,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -2382,13 +3562,13 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -2406,6 +3586,301 @@
         <v>35</v>
       </c>
       <c r="S6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" t="s">
+        <v>35</v>
+      </c>
+      <c r="S7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>23</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R9" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>23</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>16</v>
+      </c>
+      <c r="R10" t="s">
+        <v>35</v>
+      </c>
+      <c r="S10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>23</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>16</v>
+      </c>
+      <c r="R11" t="s">
+        <v>35</v>
+      </c>
+      <c r="S11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2418,22 +3893,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ABB095-35F2-4820-BA7D-AACDF5AC29ED}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2492,7 +3967,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -2524,13 +3999,13 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -2551,7 +4026,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -2583,13 +4058,13 @@
         <v>11</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -2610,7 +4085,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2642,13 +4117,13 @@
         <v>11</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -2669,7 +4144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2701,13 +4176,13 @@
         <v>11</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -2728,7 +4203,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -2760,13 +4235,13 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -2784,6 +4259,301 @@
         <v>37</v>
       </c>
       <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>37</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>23</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>37</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>11</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>37</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>11</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>23</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>37</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>11</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>23</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>37</v>
+      </c>
+      <c r="S11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2796,22 +4566,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A64BA9-AE49-4601-BDB8-368EE6FA41C6}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2870,7 +4640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -2902,13 +4672,13 @@
         <v>12</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -2929,7 +4699,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -2961,13 +4731,13 @@
         <v>12</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -2988,7 +4758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3020,13 +4790,13 @@
         <v>12</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -3047,7 +4817,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3079,13 +4849,13 @@
         <v>12</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -3106,7 +4876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -3138,13 +4908,13 @@
         <v>12</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -3162,6 +4932,301 @@
         <v>39</v>
       </c>
       <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>23</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>23</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>39</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>23</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>39</v>
+      </c>
+      <c r="S11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3173,23 +5238,23 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644856BC-020F-4C9A-8C44-C2C911A21A97}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
+    <col min="1" max="1" width="8.08984375" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="72.5546875" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="72.54296875" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3248,7 +5313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -3280,16 +5345,16 @@
         <v>13</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -3307,7 +5372,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -3339,16 +5404,16 @@
         <v>13</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -3366,7 +5431,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3398,16 +5463,16 @@
         <v>13</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -3425,7 +5490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3457,16 +5522,16 @@
         <v>13</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -3484,7 +5549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -3516,16 +5581,16 @@
         <v>13</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -3540,6 +5605,301 @@
         <v>41</v>
       </c>
       <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>21</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>21</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>41</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>21</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>41</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>21</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>41</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>21</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>41</v>
+      </c>
+      <c r="S11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3551,22 +5911,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F213CA8B-C6C2-4E7B-A814-8A18CEB0E85C}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="9.21875" customWidth="1"/>
-    <col min="8" max="8" width="74.88671875" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="8" max="8" width="74.90625" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3625,7 +5985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -3657,13 +6017,13 @@
         <v>14</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -3672,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="s">
         <v>21</v>
@@ -3684,7 +6044,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -3716,13 +6076,13 @@
         <v>14</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -3743,7 +6103,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3775,13 +6135,13 @@
         <v>14</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -3802,7 +6162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3834,13 +6194,13 @@
         <v>14</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -3861,7 +6221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -3893,13 +6253,13 @@
         <v>14</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -3917,6 +6277,301 @@
         <v>43</v>
       </c>
       <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>23</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>14</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>43</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>14</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>23</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>14</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>23</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>43</v>
+      </c>
+      <c r="S11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3928,22 +6583,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A58BA4B6-30AC-4566-AC69-57CCCF3E997A}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.77734375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.90625" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.90625" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="45" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4002,7 +6657,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -4034,16 +6689,16 @@
         <v>15</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -4061,7 +6716,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -4093,16 +6748,16 @@
         <v>15</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -4120,7 +6775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -4152,16 +6807,16 @@
         <v>15</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -4179,7 +6834,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -4211,16 +6866,16 @@
         <v>15</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -4238,7 +6893,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -4270,16 +6925,16 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -4294,6 +6949,301 @@
         <v>45</v>
       </c>
       <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>45</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>23</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>15</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>15</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>23</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>45</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>15</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>23</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4305,22 +7255,22 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C27AB6-C119-4240-85FC-9A3D905F4959}">
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.44140625" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.453125" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.88671875" customWidth="1"/>
-    <col min="9" max="9" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.90625" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4379,7 +7329,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -4411,13 +7361,13 @@
         <v>16</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>9</v>
@@ -4438,7 +7388,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -4470,13 +7420,13 @@
         <v>16</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>9</v>
@@ -4497,7 +7447,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -4529,13 +7479,13 @@
         <v>16</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>9</v>
@@ -4556,7 +7506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -4588,13 +7538,13 @@
         <v>16</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>9</v>
@@ -4615,7 +7565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -4647,13 +7597,13 @@
         <v>16</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>9</v>
@@ -4671,6 +7621,301 @@
         <v>47</v>
       </c>
       <c r="S6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>1051</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>22</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>59</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1051</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>16</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>22</v>
+      </c>
+      <c r="N8">
+        <v>23</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>47</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1051</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>16</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>22</v>
+      </c>
+      <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>47</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1051</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>16</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>22</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>47</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>1051</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>16</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>22</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>47</v>
+      </c>
+      <c r="S11" t="s">
         <v>22</v>
       </c>
     </row>
